--- a/Modules/CVMod4/CVMod4_BOM.xlsx
+++ b/Modules/CVMod4/CVMod4_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My-Dev\Modular Synth\Avalon Harmonics\CVMod4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B172294-EE9E-4E69-BECA-2154CB3FD366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A1A5D8-543E-4E9E-8A0A-5F221C367386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -125,15 +125,9 @@
     <t>Pushernut</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/black-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Gold</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/pushernuts-gold-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>M2 Screw</t>
   </si>
   <si>
@@ -275,9 +269,6 @@
     <t>https://www.tme.eu/de/en/details/l-937egw/tht-leds-3mm/kingbright-electronic/</t>
   </si>
   <si>
-    <t>https://www.tme.eu/de/en/details/zl202-80g/pin-headers/connfly/ds1021-2-40sf11/</t>
-  </si>
-  <si>
     <t>https://www.tme.eu/de/en/details/tfm-m2x10_dr211of/metal-spacers/dremec/211x10of/</t>
   </si>
   <si>
@@ -672,6 +663,15 @@
   </si>
   <si>
     <t>LED 3mm Dome Bicolor</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57164621578504</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57166910816520</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/de/en/details/zl202-10g/pin-headers/connfly/ds1021-2-5sf11-b/</t>
   </si>
 </sst>
 </file>
@@ -1575,7 +1575,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="G2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1610,19 +1610,19 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" t="s">
         <v>67</v>
       </c>
-      <c r="E3" t="s">
-        <v>70</v>
-      </c>
       <c r="F3" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1633,19 +1633,19 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L4" s="3"/>
     </row>
@@ -1657,19 +1657,19 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" t="s">
         <v>68</v>
       </c>
-      <c r="D5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" t="s">
-        <v>71</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="J5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -1680,19 +1680,19 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -1700,22 +1700,22 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -1726,19 +1726,19 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -1746,22 +1746,22 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="J9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1769,22 +1769,22 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
+        <v>85</v>
+      </c>
+      <c r="E10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="J10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -1795,13 +1795,13 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>21</v>
@@ -1812,22 +1812,22 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E12" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1838,19 +1838,19 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1858,22 +1858,22 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" t="s">
-        <v>95</v>
-      </c>
-      <c r="E14" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="J14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -1881,22 +1881,22 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C15" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" t="s">
-        <v>96</v>
-      </c>
-      <c r="E15" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="J15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1904,13 +1904,13 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E16" t="s">
         <v>13</v>
@@ -1919,7 +1919,7 @@
         <v>20</v>
       </c>
       <c r="J16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -1930,7 +1930,7 @@
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
         <v>12</v>
@@ -1939,10 +1939,10 @@
         <v>14</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="J17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -1950,19 +1950,19 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E19" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J19" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -1970,19 +1970,19 @@
         <v>2</v>
       </c>
       <c r="B20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" t="s">
         <v>47</v>
       </c>
-      <c r="C20" t="s">
+      <c r="F20" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E20" t="s">
-        <v>49</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="J20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -1990,19 +1990,19 @@
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="J21" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -2019,13 +2019,13 @@
         <v>29</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="J23" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -2033,19 +2033,19 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
         <v>29</v>
       </c>
       <c r="E24" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="J24" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -2065,7 +2065,7 @@
         <v>25</v>
       </c>
       <c r="J25" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -2076,7 +2076,7 @@
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E26" t="s">
         <v>26</v>
@@ -2085,12 +2085,12 @@
         <v>28</v>
       </c>
       <c r="J26" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -2098,32 +2098,32 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B30" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B32" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B33" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B34" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B35" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -2141,24 +2141,24 @@
     <hyperlink ref="F16" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="F11" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="F25" r:id="rId4" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="F23" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="F24" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="F26" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="F15" r:id="rId8" xr:uid="{57A67E62-1F07-4F81-BD71-0FCCC53DDD36}"/>
-    <hyperlink ref="F19" r:id="rId9" xr:uid="{386CA78F-ECAF-4BED-B017-86D6F4F05D83}"/>
-    <hyperlink ref="F20" r:id="rId10" xr:uid="{23053745-F5D1-4E91-88AD-FDB570AEC8C5}"/>
-    <hyperlink ref="F14" r:id="rId11" xr:uid="{11ED5ED0-56A5-4C20-93A1-FDAE72827046}"/>
-    <hyperlink ref="F17" r:id="rId12" xr:uid="{A893ABC8-5223-47F2-8335-C8AD6F9E7D68}"/>
-    <hyperlink ref="F12" r:id="rId13" xr:uid="{29AEA817-32F1-41F4-A924-4F4000D4818B}"/>
-    <hyperlink ref="F21" r:id="rId14" xr:uid="{43A1E3D1-40BA-485C-A829-B483D6181C61}"/>
-    <hyperlink ref="F7" r:id="rId15" xr:uid="{B40A6525-E24B-4FF5-BC67-1B758AD6314F}"/>
-    <hyperlink ref="F8" r:id="rId16" xr:uid="{3CB09C12-4D35-4819-AE80-418F9E9B256F}"/>
-    <hyperlink ref="F6" r:id="rId17" xr:uid="{5A0D7BBD-6B87-4FFB-B23E-CCF2FD9F9C1D}"/>
-    <hyperlink ref="F5" r:id="rId18" xr:uid="{B273C29C-FAF1-4C69-8A57-557C938F7138}"/>
-    <hyperlink ref="F3" r:id="rId19" xr:uid="{4CE8EB5E-E002-4130-B45B-22E26A84385B}"/>
-    <hyperlink ref="F9" r:id="rId20" xr:uid="{68290B5E-4DE3-47D4-A4E4-8D2CBBF09669}"/>
-    <hyperlink ref="F10" r:id="rId21" xr:uid="{D639F18A-B0CC-4BDF-A035-63190780DCA3}"/>
-    <hyperlink ref="F4" r:id="rId22" xr:uid="{B8A28BA1-9F88-489B-802C-B9F5F508C934}"/>
+    <hyperlink ref="F26" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="F15" r:id="rId6" xr:uid="{57A67E62-1F07-4F81-BD71-0FCCC53DDD36}"/>
+    <hyperlink ref="F19" r:id="rId7" xr:uid="{386CA78F-ECAF-4BED-B017-86D6F4F05D83}"/>
+    <hyperlink ref="F20" r:id="rId8" xr:uid="{23053745-F5D1-4E91-88AD-FDB570AEC8C5}"/>
+    <hyperlink ref="F14" r:id="rId9" xr:uid="{11ED5ED0-56A5-4C20-93A1-FDAE72827046}"/>
+    <hyperlink ref="F12" r:id="rId10" xr:uid="{29AEA817-32F1-41F4-A924-4F4000D4818B}"/>
+    <hyperlink ref="F21" r:id="rId11" xr:uid="{43A1E3D1-40BA-485C-A829-B483D6181C61}"/>
+    <hyperlink ref="F7" r:id="rId12" xr:uid="{B40A6525-E24B-4FF5-BC67-1B758AD6314F}"/>
+    <hyperlink ref="F8" r:id="rId13" xr:uid="{3CB09C12-4D35-4819-AE80-418F9E9B256F}"/>
+    <hyperlink ref="F6" r:id="rId14" xr:uid="{5A0D7BBD-6B87-4FFB-B23E-CCF2FD9F9C1D}"/>
+    <hyperlink ref="F5" r:id="rId15" xr:uid="{B273C29C-FAF1-4C69-8A57-557C938F7138}"/>
+    <hyperlink ref="F3" r:id="rId16" xr:uid="{4CE8EB5E-E002-4130-B45B-22E26A84385B}"/>
+    <hyperlink ref="F9" r:id="rId17" xr:uid="{68290B5E-4DE3-47D4-A4E4-8D2CBBF09669}"/>
+    <hyperlink ref="F10" r:id="rId18" xr:uid="{D639F18A-B0CC-4BDF-A035-63190780DCA3}"/>
+    <hyperlink ref="F4" r:id="rId19" xr:uid="{B8A28BA1-9F88-489B-802C-B9F5F508C934}"/>
+    <hyperlink ref="F23" r:id="rId20" xr:uid="{C0072B62-62BC-4582-96EA-7B992BBABAF9}"/>
+    <hyperlink ref="F24" r:id="rId21" xr:uid="{C438DAF9-FD8A-4D8E-896E-E8FCE88B09FC}"/>
+    <hyperlink ref="F17" r:id="rId22" xr:uid="{FE33FEA2-89ED-4761-824B-AD6478F2BCFF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId23"/>
